--- a/out/MLP-S4_repeat_1_000006.xlsx
+++ b/out/MLP-S4_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4867320633075707</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4867320633075707</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.791318200473974</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4867320633075707</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4867320633075707</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.191318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4867320633075707</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.191318200473974</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004204130519586615</v>
+        <v>-0.0003187095611483092</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.541104136009271</v>
+        <v>0.4102038210157579</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.791318200473974</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.083232723214529</v>
+        <v>0.8211843668648274</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1249632833411789</v>
+        <v>-0.09473302018338621</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.791318200473974</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4157204396161335</v>
+        <v>0.3151520912712235</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.791318200473974</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4157204396161335</v>
+        <v>0.3151520912712235</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.791318200473974</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4152458440446155</v>
+        <v>0.3148759057201962</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.45806023616557</v>
+        <v>0.8485017432176496</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.33426965509536</v>
+        <v>2.013568957444796</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2789833972725446</v>
+        <v>0.1623511858441944</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.191318200473974</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.43204845990755</v>
+        <v>1.488531488042106</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4886656610385877</v>
+        <v>0.2843734990823945</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.191318200473974</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.13053357570756</v>
+        <v>1.895007195012356</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2676110988192313</v>
+        <v>0.1557332766185505</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.791318200473974</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.176668953546565</v>
+        <v>1.92185517790611</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1105272811096785</v>
+        <v>0.0643203080432633</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.129831794069495</v>
+        <v>1.894598783331452</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1377079978705337</v>
+        <v>0.08013758422496202</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.294738666653533</v>
+        <v>1.990564439613833</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0829180027860095</v>
+        <v>0.04825258667233542</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.32277322582122</v>
+        <v>2.006878829586493</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.06303907480104119</v>
+        <v>0.03668583554762436</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.791318200473974</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.365899738224946</v>
+        <v>2.031976113399142</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02788314123012411</v>
+        <v>0.01622624053465855</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.358569548970514</v>
+        <v>2.027710402695124</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02212548253918613</v>
+        <v>0.01287341351847365</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.374927330826884</v>
+        <v>2.037228638609014</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01096899391511924</v>
+        <v>0.006381279112217785</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.191318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.374726451515254</v>
+        <v>2.037109638620425</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.006377786435911212</v>
+        <v>0.003710049352168924</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.191318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.376504731464048</v>
+        <v>2.038142582328087</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003186393217955606</v>
+        <v>0.001851070075711647</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.791318200473974</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.376495757964055</v>
+        <v>2.038135271395548</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001570307192985173</v>
+        <v>0.000912012763799763</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.791318200473974</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.376450846050722</v>
+        <v>2.038107023544451</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0009095168611453498</v>
+        <v>0.0005290244444644378</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.791318200473974</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.376699207464814</v>
+        <v>2.038249701122964</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0003007799056141514</v>
+        <v>0.0001735576091177526</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.376389394654329</v>
+        <v>2.038067354670754</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.000149959589161702</v>
+        <v>8.483164589084172e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.376386109316306</v>
+        <v>2.038063348677698</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.817066842368922e-05</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.376394849633731</v>
+        <v>2.038066313190443</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.529306759837545e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.376387135320979</v>
+        <v>2.038059761304713</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>2.118280671066587e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.37639181674382</v>
+        <v>2.038060139872958</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.376383814919402</v>
+        <v>2.038053472909088</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.376380710234152</v>
+        <v>2.038049610833992</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.376376391243002</v>
+        <v>2.038045063521807</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.376371567070113</v>
+        <v>2.038045153466457</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.376370709136529</v>
+        <v>2.038044295532872</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.376370937457563</v>
+        <v>2.038044523853906</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.376370141793352</v>
+        <v>2.038043728189695</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.376370204062725</v>
+        <v>2.038043790459068</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.376370231738001</v>
+        <v>2.038043818134345</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.376370383952024</v>
+        <v>2.038043970348367</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.376370038011063</v>
+        <v>2.038043624407406</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.376370114118074</v>
+        <v>2.038043700514418</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.376370280169736</v>
+        <v>2.038043866566079</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.376370639948336</v>
+        <v>2.038044226344679</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.376370660704793</v>
+        <v>2.038044247101137</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.376370764487082</v>
+        <v>2.038044350883425</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.376370992808117</v>
+        <v>2.03804457920446</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.376370868269371</v>
+        <v>2.038044454665714</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.376370895944647</v>
+        <v>2.038044482340991</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.376370951295202</v>
+        <v>2.038044537691545</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.376371214210332</v>
+        <v>2.038044800606675</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.376371131184502</v>
+        <v>2.038044717580845</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.376370923619925</v>
+        <v>2.038044510016268</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.376370937457563</v>
+        <v>2.038044523853906</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.376371075833947</v>
+        <v>2.038044662230291</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.37637079216236</v>
+        <v>2.038044378558702</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.376370619191878</v>
+        <v>2.038044205588222</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.37637051540959</v>
+        <v>2.038044101805933</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.376370660704793</v>
+        <v>2.038044247101137</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.376370902863467</v>
+        <v>2.03804448925981</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.376370729892986</v>
+        <v>2.03804431628933</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.376370432383759</v>
+        <v>2.038044018780103</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.376370418546121</v>
+        <v>2.038044004942464</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.376370051848701</v>
+        <v>2.038043638245044</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.376370051848701</v>
+        <v>2.038043638245044</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.376369989579328</v>
+        <v>2.038043575975671</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.37636988579704</v>
+        <v>2.038043472193383</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.37636971282656</v>
+        <v>2.038043299222902</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.376369761258294</v>
+        <v>2.038043347654637</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.376369401479693</v>
+        <v>2.038042987876037</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.376369359966778</v>
+        <v>2.038042946363121</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.376369415317332</v>
+        <v>2.038043001713675</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.376369470667886</v>
+        <v>2.038043057064229</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.376369512180801</v>
+        <v>2.038043098577145</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.376369242346851</v>
+        <v>2.038042828743194</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.376369297697405</v>
+        <v>2.038042884093748</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.376369442992609</v>
+        <v>2.038043029388952</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.376369408398513</v>
+        <v>2.038042994794856</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.376369394560875</v>
+        <v>2.038042980957218</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.376369484505524</v>
+        <v>2.038043070901868</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.791318200473974</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.376369802771209</v>
+        <v>2.038043389167552</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4867320633075707</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.376369622881909</v>
+        <v>2.038043209278252</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4867320633075707</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.376369664394825</v>
+        <v>2.038043250791167</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.376369477586705</v>
+        <v>2.038043063983048</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.376369546774898</v>
+        <v>2.03804313317124</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.37636934612914</v>
+        <v>2.038042932525483</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.086732063307571</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.376369387642055</v>
+        <v>2.038042974038398</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.086732063307571</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.376369415317332</v>
+        <v>2.038043001713675</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_1_000006.xlsx
+++ b/out/MLP-S4_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.791318200473974</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4867320633075707</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4867320633075707</v>
+        <v>-0.3794734148394771</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.3794734148394771</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820189</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.791318200473974</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4867320633075707</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.791318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.791318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4867320633075707</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.791318200473974</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820189</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820189</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.191318200473974</v>
+        <v>0.9190638486035149</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.791318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4867320633075707</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.791318200473974</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820189</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.191318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004204130519586615</v>
+        <v>-0.0003144642711671768</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.541104136009271</v>
+        <v>0.4047398021178412</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.083232723214529</v>
+        <v>0.8102459885168934</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1249632833411789</v>
+        <v>-0.09347115363103027</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4157204396161335</v>
+        <v>0.3109541842156437</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4157204396161335</v>
+        <v>0.3109541842156437</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.791318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4152458440446155</v>
+        <v>0.3106994569302802</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.45806023616557</v>
+        <v>0.7825773103341948</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.9190638486035149</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.33426965509536</v>
+        <v>1.877412371933719</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2789833972725446</v>
+        <v>0.1497373505223635</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.191318200473974</v>
+        <v>0.9190638486035149</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.43204845990755</v>
+        <v>1.393167744212864</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4886656610385877</v>
+        <v>0.262279170244165</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.191318200473974</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.13053357570756</v>
+        <v>1.768062134276548</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2676110988192313</v>
+        <v>0.1436333798589609</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.791318200473974</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.176668953546565</v>
+        <v>1.792824131914169</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1105272811096785</v>
+        <v>0.05932287446727912</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.129831794069495</v>
+        <v>1.767685451410719</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1377079978705337</v>
+        <v>0.07391121084014067</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.294738666653533</v>
+        <v>1.85619495570259</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0829180027860095</v>
+        <v>0.04450350561928916</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.32277322582122</v>
+        <v>1.871241782165824</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.06303907480104119</v>
+        <v>0.03383552608840181</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.791318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.365899738224946</v>
+        <v>1.894389130141271</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02788314123012411</v>
+        <v>0.01496454196552955</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820189</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.358569548970514</v>
+        <v>1.890454640620057</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02212548253918613</v>
+        <v>0.01187461764042516</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820189</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.374927330826884</v>
+        <v>1.899233432594834</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01096899391511924</v>
+        <v>0.005885986020083387</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.191318200473974</v>
+        <v>0.9190638486035149</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.374726451515254</v>
+        <v>1.899123293115136</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.006377786435911212</v>
+        <v>0.00341912927760597</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.191318200473974</v>
+        <v>1.668332480325011</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.376504731464048</v>
+        <v>1.900075365181319</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003186393217955606</v>
+        <v>0.0017085192391758</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.376495757964055</v>
+        <v>1.900068231734194</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001570307192985173</v>
+        <v>0.0008401465597402205</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.791318200473974</v>
+        <v>1.868332480325011</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.376450846050722</v>
+        <v>1.900041803103865</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0009095168611453498</v>
+        <v>0.0004856349583517023</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.791318200473974</v>
+        <v>1.119063848603515</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.376699207464814</v>
+        <v>1.900172945440012</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0003007799056141514</v>
+        <v>0.0001601657884339212</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.1697952168820189</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.376389394654329</v>
+        <v>1.900003899971718</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.000149959589161702</v>
+        <v>7.809427244902859e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.376386109316306</v>
+        <v>1.899999819428141</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.817066842368922e-05</v>
+        <v>3.903153034195311e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.376394849633731</v>
+        <v>1.900002188135369</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.529306759837545e-05</v>
+        <v>1.633162402266935e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.376387135320979</v>
+        <v>1.899995715331201</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>2.118280671066587e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.37639181674382</v>
+        <v>1.899996093899446</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.376383814919402</v>
+        <v>1.899989426935576</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.376380710234152</v>
+        <v>1.89998556486048</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.376376391243002</v>
+        <v>1.899981017548295</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.376371567070113</v>
+        <v>1.899981107492945</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.376370709136529</v>
+        <v>1.89998024955936</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.376370937457563</v>
+        <v>1.899980477880395</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.376370141793352</v>
+        <v>1.899979682216183</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.376370204062725</v>
+        <v>1.899979744485556</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.376370231738001</v>
+        <v>1.899979772160833</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.376370383952024</v>
+        <v>1.899979924374856</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.376370038011063</v>
+        <v>1.899979578433894</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.376370114118074</v>
+        <v>1.899979654540906</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.376370280169736</v>
+        <v>1.899979820592567</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.376370639948336</v>
+        <v>1.899980180371167</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.376370660704793</v>
+        <v>1.899980201127625</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.376370764487082</v>
+        <v>1.899980304909913</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.376370992808117</v>
+        <v>1.899980533230948</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.376370868269371</v>
+        <v>1.899980408692202</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.376370895944647</v>
+        <v>1.899980436367479</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.376370951295202</v>
+        <v>1.899980491718033</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.376371214210332</v>
+        <v>1.899980754633164</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.376371131184502</v>
+        <v>1.899980671607333</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.376370923619925</v>
+        <v>1.899980464042756</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.376370937457563</v>
+        <v>1.899980477880395</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.376371075833947</v>
+        <v>1.899980616256779</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.37637079216236</v>
+        <v>1.899980332585191</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.376370619191878</v>
+        <v>1.89998015961471</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.37637051540959</v>
+        <v>1.899980055832421</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.376370660704793</v>
+        <v>1.899980201127625</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.376370902863467</v>
+        <v>1.899980443286298</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.376370729892986</v>
+        <v>1.899980270315818</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.376370432383759</v>
+        <v>1.899979972806591</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.376370418546121</v>
+        <v>1.899979958968952</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.376370051848701</v>
+        <v>1.899979592271532</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.376370051848701</v>
+        <v>1.899979592271532</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.376369989579328</v>
+        <v>1.89997953000216</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.37636988579704</v>
+        <v>1.899979426219871</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.37636971282656</v>
+        <v>1.89997925324939</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.376369761258294</v>
+        <v>1.899979301681125</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.376369401479693</v>
+        <v>1.899978941902525</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.376369359966778</v>
+        <v>1.899978900389609</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.376369415317332</v>
+        <v>1.899978955740163</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.376369470667886</v>
+        <v>1.899979011090717</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.376369512180801</v>
+        <v>1.899979052603633</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.376369242346851</v>
+        <v>1.899978782769682</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.376369297697405</v>
+        <v>1.899978838120236</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.376369442992609</v>
+        <v>1.89997898341544</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.376369408398513</v>
+        <v>1.899978948821344</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.376369394560875</v>
+        <v>1.899978934983706</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.086732063307571</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.376369484505524</v>
+        <v>1.899979024928356</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.791318200473974</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.376369802771209</v>
+        <v>1.89997934319404</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4867320633075707</v>
+        <v>0.369795216882019</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.376369622881909</v>
+        <v>1.89997916330474</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4867320633075707</v>
+        <v>-0.3794734148394771</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.376369664394825</v>
+        <v>1.899979204817656</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.3794734148394771</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.376369477586705</v>
+        <v>1.899979018009536</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.376369546774898</v>
+        <v>1.899979087197728</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.37636934612914</v>
+        <v>1.899978886551971</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.376369387642055</v>
+        <v>1.899978928064886</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.086732063307571</v>
+        <v>-0.5794734148394771</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.376369415317332</v>
+        <v>1.899978955740163</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_1_000006.xlsx
+++ b/out/MLP-S4_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3997767269611359</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.7200000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4082886874675751</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4369827806949615</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4735791683197021</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4238386750221252</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4598499238491058</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4027091860771179</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4787405133247375</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4812528192996979</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.429829478263855</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4043469727039337</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3887393772602081</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4453804492950439</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3987902104854584</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.3936036229133606</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3952779173851013</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4335890710353851</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4639872908592224</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.369795216882019</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5175999402999878</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.369795216882019</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4584754407405853</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.369795216882019</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4483489096164703</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3794734148394771</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4181903004646301</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3794734148394771</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4316418170928955</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1697952168820189</v>
+        <v>0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5100538730621338</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.369795216882019</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4388040006160736</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.119063848603515</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5401615500450134</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.119063848603515</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.6747826933860779</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.868332480325011</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.570932924747467</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.119063848603515</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4920627474784851</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.119063848603515</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5001721978187561</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.369795216882019</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4445839822292328</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1697952168820189</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4152311682701111</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.440374344587326</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1697952168820189</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5907488465309143</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9190638486035149</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.5009825825691223</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.119063848603515</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4799103736877441</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.119063848603515</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5198162198066711</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.369795216882019</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.452590137720108</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.369795216882019</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4828063547611237</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.1697952168820189</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5216761827468872</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.119063848603515</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5844683647155762</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.868332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6098615527153015</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.868332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.6853823065757751</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.868332480325011</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003144642711671768</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4047398021178412</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6486546993255615</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.868332480325011</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8102459885168934</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09347115363103027</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5233724117279053</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.868332480325011</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3109541842156437</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5752763748168945</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.868332480325011</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3109541842156437</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.564003050327301</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.119063848603515</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3106994569302802</v>
+        <v>0.2123013248989449</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.7825773103341948</v>
+        <v>0.2783048746353901</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4961978793144226</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9190638486035149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.877412371933719</v>
+        <v>0.7694652442227462</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1497373505223635</v>
+        <v>0.05325043982180468</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.590564489364624</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9190638486035149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.393167744212864</v>
+        <v>0.5972552420977619</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.262279170244165</v>
+        <v>0.09327319551786681</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5554827451705933</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.668332480325011</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.768062134276548</v>
+        <v>0.7305776076146511</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1436333798589609</v>
+        <v>0.05108003439471832</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5669409036636353</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.668332480325011</v>
+        <v>-0.16</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.792824131914169</v>
+        <v>0.739383649579078</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.05932287446727912</v>
+        <v>0.0210966012868973</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5020204186439514</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.868332480325011</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.767685451410719</v>
+        <v>0.7304436639571162</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07391121084014067</v>
+        <v>0.02628455481512958</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6633331775665283</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.868332480325011</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.85619495570259</v>
+        <v>0.7619203013701816</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04450350561928916</v>
+        <v>0.01582669723685154</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5085416436195374</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.868332480325011</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.871241782165824</v>
+        <v>0.7672715049972902</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03383552608840181</v>
+        <v>0.01203227068582927</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.7274575233459473</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.119063848603515</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.894389130141271</v>
+        <v>0.7755025763967033</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01496454196552955</v>
+        <v>0.005319128419633081</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3954262733459473</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1697952168820189</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.890454640620057</v>
+        <v>0.7741000719318202</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01187461764042516</v>
+        <v>0.004219704787200033</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3210653960704803</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1697952168820189</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.899233432594834</v>
+        <v>0.777218819608625</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005885986020083387</v>
+        <v>0.002088738980386324</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.8274957537651062</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9190638486035149</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.899123293115136</v>
+        <v>0.7771764308077908</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00341912927760597</v>
+        <v>0.001213955112418778</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.777500331401825</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.668332480325011</v>
+        <v>0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.900075365181319</v>
+        <v>0.7775119933868905</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0017085192391758</v>
+        <v>0.0006030229558365741</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.550114631652832</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.868332480325011</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.900068231734194</v>
+        <v>0.7775062363572656</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008401465597402205</v>
+        <v>0.0002968380570500788</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5212007164955139</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.868332480325011</v>
+        <v>0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.900041803103865</v>
+        <v>0.7774935956300393</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004856349583517023</v>
+        <v>0.0001685579444509423</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.6124274134635925</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.119063848603515</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.900172945440012</v>
+        <v>0.7775370544039446</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001601657884339212</v>
+        <v>5.303122296326961e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4379102885723114</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1697952168820189</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.900003899971718</v>
+        <v>0.7774733097958993</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.809427244902859e-05</v>
+        <v>2.419528491452356e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3867473602294922</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.899999819428141</v>
+        <v>0.7774686466857942</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.903153034195311e-05</v>
+        <v>1.212337291075954e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3653604090213776</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.900002188135369</v>
+        <v>0.777466434265255</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.633162402266935e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4224546551704407</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.899995715331201</v>
+        <v>0.7774608925925246</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4629366397857666</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.899996093899446</v>
+        <v>0.7774580440198228</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.3943702578544617</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.899989426935576</v>
+        <v>0.777452376589549</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4592150449752808</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.89998556486048</v>
+        <v>0.7774527571246067</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4106959700584412</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.899981017548295</v>
+        <v>0.7774529854456415</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3961734771728516</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.899981107492945</v>
+        <v>0.7774530753902914</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.336897611618042</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.89998024955936</v>
+        <v>0.7774522174567066</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3944782316684723</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.899980477880395</v>
+        <v>0.7774524457777413</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3909999430179596</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.899979682216183</v>
+        <v>0.7774516501135296</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.2752722799777985</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.899979744485556</v>
+        <v>0.7774517123829027</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3152795433998108</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.899979772160833</v>
+        <v>0.7774517400581795</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.411420464515686</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.899979924374856</v>
+        <v>0.7774518922722028</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3355298042297363</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.899979578433894</v>
+        <v>0.777451546331241</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3466819822788239</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.899979654540906</v>
+        <v>0.7774516224382527</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3089999556541443</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.899979820592567</v>
+        <v>0.7774517884899143</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4366209506988525</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.899980180371167</v>
+        <v>0.7774521482685143</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4603359401226044</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.899980201127625</v>
+        <v>0.7774521690249721</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4695706367492676</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.899980304909913</v>
+        <v>0.7774522728072605</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.3782473504543304</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.899980533230948</v>
+        <v>0.7774525011282952</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3644008934497833</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.899980408692202</v>
+        <v>0.777452376589549</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3626088798046112</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.899980436367479</v>
+        <v>0.7774524042648259</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4480955600738525</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.899980491718033</v>
+        <v>0.7774524596153798</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3669419884681702</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.899980754633164</v>
+        <v>0.7774527225305106</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3788794875144958</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.899980671607333</v>
+        <v>0.7774526395046797</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3413245677947998</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.899980464042756</v>
+        <v>0.7774524319401029</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3464930057525635</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.899980477880395</v>
+        <v>0.7774524457777413</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3497123420238495</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.899980616256779</v>
+        <v>0.777452584154126</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3549870550632477</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.899980332585191</v>
+        <v>0.7774523004825373</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3305473923683167</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.89998015961471</v>
+        <v>0.7774521275120566</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3870026767253876</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.899980055832421</v>
+        <v>0.7774520237297681</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3476283848285675</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.899980201127625</v>
+        <v>0.7774521690249721</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3214878737926483</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.899980443286298</v>
+        <v>0.7774524111836453</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3259649276733398</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.899980270315818</v>
+        <v>0.7774522382131642</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.2879733145236969</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.899979972806591</v>
+        <v>0.7774519407039373</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3131940066814423</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.899979958968952</v>
+        <v>0.7774519268662988</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.2825383841991425</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.899979592271532</v>
+        <v>0.7774515601688796</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.317407101392746</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.899979592271532</v>
+        <v>0.7774515601688796</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3705258667469025</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.89997953000216</v>
+        <v>0.7774514978995065</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2969456911087036</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.899979426219871</v>
+        <v>0.777451394117218</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3153783977031708</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.89997925324939</v>
+        <v>0.7774512211467373</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.319945216178894</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.899979301681125</v>
+        <v>0.7774512695784718</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3064371049404144</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.899978941902525</v>
+        <v>0.7774509097998717</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.2874793708324432</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.899978900389609</v>
+        <v>0.7774508682869563</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3424881100654602</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.899978955740163</v>
+        <v>0.77745092363751</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3153164982795715</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.899979011090717</v>
+        <v>0.777450978988064</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3092366755008698</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.899979052603633</v>
+        <v>0.7774510205009794</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3107653260231018</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.899978782769682</v>
+        <v>0.7774507506670293</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3277828395366669</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.899978838120236</v>
+        <v>0.7774508060175832</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3184697926044464</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.89997898341544</v>
+        <v>0.7774509513127872</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3306009769439697</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.899978948821344</v>
+        <v>0.7774509167186909</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3134466707706451</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.899978934983706</v>
+        <v>0.7774509028810523</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3745304346084595</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.369795216882019</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.899979024928356</v>
+        <v>0.7774509928257025</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5028295516967773</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.369795216882019</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.89997934319404</v>
+        <v>0.7774513110913872</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3635112643241882</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.369795216882019</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.89997916330474</v>
+        <v>0.7774511312020871</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3361481428146362</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3794734148394771</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.899979204817656</v>
+        <v>0.7774511727150024</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3496215343475342</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3794734148394771</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.899979018009536</v>
+        <v>0.7774509859068831</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3086017072200775</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5794734148394771</v>
+        <v>0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.899979087197728</v>
+        <v>0.7774510550950756</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3356252014636993</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.899978886551971</v>
+        <v>0.7774508544493178</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3072536885738373</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.899978928064886</v>
+        <v>0.7774508959622332</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.3475979268550873</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5794734148394771</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.899978955740163</v>
+        <v>0.77745092363751</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_1_000006.xlsx
+++ b/out/MLP-S4_repeat_1_000006.xlsx
@@ -65339,7 +65339,7 @@
         <v>0.3089999556541443</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0.7774517884899143</v>
@@ -66134,7 +66134,7 @@
         <v>0.4366209506988525</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
         <v>0.7774521482685143</v>
@@ -66929,7 +66929,7 @@
         <v>0.4603359401226044</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
         <v>0.7774521690249721</v>
@@ -67724,7 +67724,7 @@
         <v>0.4695706367492676</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
         <v>0.7774522728072605</v>
@@ -68519,7 +68519,7 @@
         <v>0.3782473504543304</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
         <v>0.7774525011282952</v>
